--- a/data/trans_orig/P16A04-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A04-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18651</t>
+          <t>19126</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>9247</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21852</t>
+          <t>23008</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>455125</t>
+          <t>454650</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>469230</t>
+          <t>468884</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298017</t>
+          <t>297433</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>305733</t>
+          <t>305732</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>758605</t>
+          <t>757449</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>773645</t>
+          <t>772855</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>10056</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17520</t>
+          <t>17923</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22771</t>
+          <t>21538</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>356192</t>
+          <t>356878</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365926</t>
+          <t>365920</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>354345</t>
+          <t>353942</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367043</t>
+          <t>366899</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>716028</t>
+          <t>717261</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731452</t>
+          <t>731351</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>15674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23712</t>
+          <t>22670</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>526528</t>
+          <t>526715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>538009</t>
+          <t>537874</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156030</t>
+          <t>155525</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165538</t>
+          <t>165679</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>686459</t>
+          <t>687501</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>701651</t>
+          <t>701733</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14528</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34386</t>
+          <t>34096</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13740</t>
+          <t>13466</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31684</t>
+          <t>31770</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33448</t>
+          <t>32820</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58414</t>
+          <t>59443</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1203948</t>
+          <t>1204238</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1223806</t>
+          <t>1224035</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>682601</t>
+          <t>682515</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>700545</t>
+          <t>700819</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1894206</t>
+          <t>1893177</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1919172</t>
+          <t>1919800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18191</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22248</t>
+          <t>23111</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16055</t>
+          <t>15831</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34503</t>
+          <t>34602</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>331346</t>
+          <t>331638</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>344122</t>
+          <t>344010</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>546504</t>
+          <t>545641</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>561896</t>
+          <t>561869</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>883786</t>
+          <t>883687</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>902234</t>
+          <t>902458</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13912</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32353</t>
+          <t>33273</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15694</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36489</t>
+          <t>36196</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>291353</t>
+          <t>291345</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1216407</t>
+          <t>1215487</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1234848</t>
+          <t>1234640</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1510471</t>
+          <t>1510764</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1531266</t>
+          <t>1531222</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45492</t>
+          <t>44609</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>75694</t>
+          <t>75916</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58613</t>
+          <t>58568</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92461</t>
+          <t>93290</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>113043</t>
+          <t>112257</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>158522</t>
+          <t>156222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3193478</t>
+          <t>3193256</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3223680</t>
+          <t>3224563</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3285663</t>
+          <t>3284834</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3319511</t>
+          <t>3319556</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6488774</t>
+          <t>6491074</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6534253</t>
+          <t>6535039</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22517</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15274</t>
+          <t>15254</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11196</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32428</t>
+          <t>31418</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412502</t>
+          <t>413195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>429828</t>
+          <t>429895</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>299180</t>
+          <t>299200</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311455</t>
+          <t>310795</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>717045</t>
+          <t>718055</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>738277</t>
+          <t>738562</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15480</t>
+          <t>16033</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14731</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8791</t>
+          <t>8547</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24362</t>
+          <t>24302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401538</t>
+          <t>400985</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>413195</t>
+          <t>413793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>320584</t>
+          <t>321813</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>332212</t>
+          <t>332106</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>727971</t>
+          <t>728031</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>743542</t>
+          <t>743786</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36533</t>
+          <t>36216</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14519</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19604</t>
+          <t>19599</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45216</t>
+          <t>45080</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>589805</t>
+          <t>590122</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>612268</t>
+          <t>612718</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>244461</t>
+          <t>244496</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>255910</t>
+          <t>255834</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>840102</t>
+          <t>840238</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>865714</t>
+          <t>865719</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24708</t>
+          <t>23328</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51304</t>
+          <t>49549</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23061</t>
+          <t>24733</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47518</t>
+          <t>49510</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54820</t>
+          <t>54068</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91006</t>
+          <t>89672</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1105117</t>
+          <t>1106872</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1131713</t>
+          <t>1133093</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>718142</t>
+          <t>716150</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>742599</t>
+          <t>740927</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1831075</t>
+          <t>1832409</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1867261</t>
+          <t>1868013</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>9492</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26934</t>
+          <t>25352</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9316</t>
+          <t>10068</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27298</t>
+          <t>27871</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21985</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45360</t>
+          <t>45098</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>483662</t>
+          <t>485244</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>501269</t>
+          <t>501104</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>731070</t>
+          <t>730497</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>749052</t>
+          <t>748300</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1223604</t>
+          <t>1223866</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1246979</t>
+          <t>1246546</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>7016</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19783</t>
+          <t>19703</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39979</t>
+          <t>41214</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20909</t>
+          <t>20571</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42791</t>
+          <t>43176</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256379</t>
+          <t>258825</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1065277</t>
+          <t>1064042</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1085473</t>
+          <t>1085553</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1328307</t>
+          <t>1327922</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1350189</t>
+          <t>1350527</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>76767</t>
+          <t>77511</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>120224</t>
+          <t>120940</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>82106</t>
+          <t>80971</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>123943</t>
+          <t>122577</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>171328</t>
+          <t>173005</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>228404</t>
+          <t>231659</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3291010</t>
+          <t>3290294</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3334467</t>
+          <t>3333723</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3414090</t>
+          <t>3415456</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3455927</t>
+          <t>3457062</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6720863</t>
+          <t>6717608</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6777939</t>
+          <t>6776262</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23171</t>
+          <t>22005</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11714</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>10779</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28839</t>
+          <t>29730</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>405921</t>
+          <t>407087</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>421913</t>
+          <t>421705</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>335341</t>
+          <t>334613</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>345946</t>
+          <t>345949</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>747308</t>
+          <t>746417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>765292</t>
+          <t>765368</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14396</t>
+          <t>14643</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11780</t>
+          <t>11627</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20547</t>
+          <t>20034</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>362831</t>
+          <t>362584</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>374091</t>
+          <t>374113</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>360493</t>
+          <t>360646</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371203</t>
+          <t>371047</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>728953</t>
+          <t>729466</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>743074</t>
+          <t>743331</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12614</t>
+          <t>12520</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16213</t>
+          <t>15542</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23759</t>
+          <t>22870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>509300</t>
+          <t>509394</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519780</t>
+          <t>519749</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149910</t>
+          <t>150581</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163067</t>
+          <t>163153</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>664277</t>
+          <t>665166</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>680573</t>
+          <t>680636</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18086</t>
+          <t>17744</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38030</t>
+          <t>38526</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19183</t>
+          <t>17965</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39852</t>
+          <t>39219</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39187</t>
+          <t>39695</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68402</t>
+          <t>69470</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1111608</t>
+          <t>1111112</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1131552</t>
+          <t>1131894</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>786024</t>
+          <t>786657</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>806693</t>
+          <t>807911</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1907112</t>
+          <t>1906044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1936327</t>
+          <t>1935819</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22460</t>
+          <t>22458</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10409</t>
+          <t>10849</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27326</t>
+          <t>27367</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20503</t>
+          <t>20285</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42896</t>
+          <t>43470</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>598246</t>
+          <t>598248</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>614374</t>
+          <t>614019</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>710918</t>
+          <t>710877</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>727835</t>
+          <t>727395</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1316054</t>
+          <t>1315480</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1338447</t>
+          <t>1338665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>7992</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10295</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26970</t>
+          <t>27916</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12782</t>
+          <t>13282</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31814</t>
+          <t>31347</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279209</t>
+          <t>279153</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286213</t>
+          <t>286212</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1055055</t>
+          <t>1054109</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1071730</t>
+          <t>1071612</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1337356</t>
+          <t>1337823</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1356388</t>
+          <t>1355888</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54543</t>
+          <t>52556</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88346</t>
+          <t>85737</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>63334</t>
+          <t>62800</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>101227</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>125308</t>
+          <t>126693</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>176326</t>
+          <t>177745</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3297376</t>
+          <t>3299985</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3331179</t>
+          <t>3333166</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3430369</t>
+          <t>3431247</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3468262</t>
+          <t>3468796</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6740992</t>
+          <t>6739573</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6792010</t>
+          <t>6790625</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3604</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14095</t>
+          <t>14397</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>26326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17906</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35867</t>
+          <t>36131</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>491117</t>
+          <t>490815</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>501608</t>
+          <t>501337</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>419414</t>
+          <t>421141</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>436042</t>
+          <t>435725</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>916812</t>
+          <t>916548</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>934773</t>
+          <t>935150</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>13875</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11950</t>
+          <t>12079</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8553</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22107</t>
+          <t>22556</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>438690</t>
+          <t>438338</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>448800</t>
+          <t>448860</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>370630</t>
+          <t>370501</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>379388</t>
+          <t>379326</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>812686</t>
+          <t>812237</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>826406</t>
+          <t>826240</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37057</t>
+          <t>39539</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13868</t>
+          <t>13476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>10950</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46866</t>
+          <t>46144</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>631207</t>
+          <t>628725</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662813</t>
+          <t>663096</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153043</t>
+          <t>153435</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162105</t>
+          <t>162242</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>788309</t>
+          <t>789031</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>825583</t>
+          <t>824225</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>13343</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31155</t>
+          <t>32089</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>9766</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31454</t>
+          <t>31989</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27888</t>
+          <t>28103</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58095</t>
+          <t>57068</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1003664</t>
+          <t>1002730</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1021322</t>
+          <t>1021476</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>945743</t>
+          <t>945208</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>967296</t>
+          <t>967431</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1953921</t>
+          <t>1954948</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1984128</t>
+          <t>1983913</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15890</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22543</t>
+          <t>23074</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52531</t>
+          <t>57017</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31254</t>
+          <t>31047</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62178</t>
+          <t>64125</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>457669</t>
+          <t>456989</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>468716</t>
+          <t>468794</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>786465</t>
+          <t>781979</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>816453</t>
+          <t>815922</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1250377</t>
+          <t>1248430</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1281301</t>
+          <t>1281508</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22131</t>
+          <t>23872</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>12078</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26199</t>
+          <t>26039</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18237</t>
+          <t>17632</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42661</t>
+          <t>40606</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>218376</t>
+          <t>216635</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238263</t>
+          <t>237858</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>733953</t>
+          <t>734113</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>747857</t>
+          <t>748074</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>957998</t>
+          <t>960053</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>982422</t>
+          <t>983027</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53864</t>
+          <t>53336</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94792</t>
+          <t>97865</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84086</t>
+          <t>83741</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>129461</t>
+          <t>130245</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>151550</t>
+          <t>149790</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>214195</t>
+          <t>212179</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3279782</t>
+          <t>3276709</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3320710</t>
+          <t>3321238</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3443842</t>
+          <t>3443058</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3489217</t>
+          <t>3489562</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6733682</t>
+          <t>6735698</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6796327</t>
+          <t>6798087</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A04-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A04-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19126</t>
+          <t>18782</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9247</t>
+          <t>9538</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23008</t>
+          <t>22669</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>454650</t>
+          <t>454994</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>468884</t>
+          <t>468853</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>297433</t>
+          <t>297142</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>305732</t>
+          <t>305738</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>757449</t>
+          <t>757788</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>772855</t>
+          <t>773057</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>896</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>9696</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17923</t>
+          <t>17643</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7448</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21538</t>
+          <t>22045</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>356878</t>
+          <t>357238</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365920</t>
+          <t>366038</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>353942</t>
+          <t>354222</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366899</t>
+          <t>366929</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>717261</t>
+          <t>716754</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731351</t>
+          <t>731441</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15674</t>
+          <t>15269</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12257</t>
+          <t>12388</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8319</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22670</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>526715</t>
+          <t>527120</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>537874</t>
+          <t>538088</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155525</t>
+          <t>155394</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165679</t>
+          <t>165744</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>687501</t>
+          <t>686828</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>701733</t>
+          <t>701852</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14299</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>34536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13466</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31770</t>
+          <t>30794</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32820</t>
+          <t>32514</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59443</t>
+          <t>59166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1204238</t>
+          <t>1203798</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1224035</t>
+          <t>1223034</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>682515</t>
+          <t>683491</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>700819</t>
+          <t>700882</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1893177</t>
+          <t>1893454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1919800</t>
+          <t>1920106</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5455</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17899</t>
+          <t>17983</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23111</t>
+          <t>24002</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15831</t>
+          <t>15754</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34602</t>
+          <t>36116</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>331638</t>
+          <t>331554</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>344010</t>
+          <t>344082</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>545641</t>
+          <t>544750</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>561869</t>
+          <t>561465</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>883687</t>
+          <t>882173</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>902458</t>
+          <t>902535</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33273</t>
+          <t>33409</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>15988</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36196</t>
+          <t>34972</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>291345</t>
+          <t>291154</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1215487</t>
+          <t>1215351</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1234640</t>
+          <t>1234226</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1510764</t>
+          <t>1511988</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1531222</t>
+          <t>1530972</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44609</t>
+          <t>44589</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>75916</t>
+          <t>76267</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58568</t>
+          <t>58840</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>93290</t>
+          <t>95468</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>112257</t>
+          <t>112044</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>156222</t>
+          <t>158071</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3193256</t>
+          <t>3192905</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3224563</t>
+          <t>3224583</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3284834</t>
+          <t>3282656</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3319556</t>
+          <t>3319284</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6491074</t>
+          <t>6489225</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6535039</t>
+          <t>6535252</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21824</t>
+          <t>22680</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15254</t>
+          <t>16053</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10911</t>
+          <t>10625</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31418</t>
+          <t>30955</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413195</t>
+          <t>412339</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>429895</t>
+          <t>429308</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>299200</t>
+          <t>298401</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310795</t>
+          <t>311483</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>718055</t>
+          <t>718518</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>738562</t>
+          <t>738848</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16033</t>
+          <t>16067</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>8962</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24302</t>
+          <t>24415</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>400985</t>
+          <t>400951</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>413793</t>
+          <t>413059</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>321813</t>
+          <t>321993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>332106</t>
+          <t>332276</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>728031</t>
+          <t>727918</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>743786</t>
+          <t>743371</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13036</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36216</t>
+          <t>37489</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19599</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45080</t>
+          <t>45930</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>590122</t>
+          <t>588849</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>612718</t>
+          <t>613302</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>244496</t>
+          <t>245042</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>255834</t>
+          <t>255828</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>840238</t>
+          <t>839388</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>865719</t>
+          <t>865219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23328</t>
+          <t>24593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49549</t>
+          <t>49783</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24733</t>
+          <t>23219</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49510</t>
+          <t>49297</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54068</t>
+          <t>53472</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89672</t>
+          <t>90286</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1106872</t>
+          <t>1106638</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1133093</t>
+          <t>1131828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>716150</t>
+          <t>716363</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>740927</t>
+          <t>742441</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1832409</t>
+          <t>1831795</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1868013</t>
+          <t>1868609</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9492</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25352</t>
+          <t>26664</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27871</t>
+          <t>27435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22418</t>
+          <t>22803</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45098</t>
+          <t>47065</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>485244</t>
+          <t>483932</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>501104</t>
+          <t>500292</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>730497</t>
+          <t>730933</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>748300</t>
+          <t>749407</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1223866</t>
+          <t>1221899</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1246546</t>
+          <t>1246161</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7016</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19703</t>
+          <t>18823</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41214</t>
+          <t>40175</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20571</t>
+          <t>20937</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43176</t>
+          <t>43159</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258825</t>
+          <t>258032</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1064042</t>
+          <t>1065081</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1085553</t>
+          <t>1086433</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1327922</t>
+          <t>1327939</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1350527</t>
+          <t>1350161</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77511</t>
+          <t>77377</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>120940</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80971</t>
+          <t>83766</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>122577</t>
+          <t>122769</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>173005</t>
+          <t>168502</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>231659</t>
+          <t>229411</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3290294</t>
+          <t>3290245</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3333723</t>
+          <t>3333857</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3415456</t>
+          <t>3415264</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3457062</t>
+          <t>3454267</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6717608</t>
+          <t>6719856</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6776262</t>
+          <t>6780765</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22005</t>
+          <t>23825</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>12893</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10779</t>
+          <t>10634</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29730</t>
+          <t>29335</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>407087</t>
+          <t>405267</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>421705</t>
+          <t>421892</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>334613</t>
+          <t>334162</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>345949</t>
+          <t>345942</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>746417</t>
+          <t>746812</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>765368</t>
+          <t>765513</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14643</t>
+          <t>14694</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11627</t>
+          <t>10978</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20034</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>362584</t>
+          <t>362533</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>374113</t>
+          <t>374253</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>360646</t>
+          <t>361295</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371047</t>
+          <t>371022</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>729466</t>
+          <t>728124</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>743331</t>
+          <t>743617</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12520</t>
+          <t>13129</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15542</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22870</t>
+          <t>23206</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>509394</t>
+          <t>508785</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519749</t>
+          <t>519844</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150581</t>
+          <t>149122</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163153</t>
+          <t>162967</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>665166</t>
+          <t>664830</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>680636</t>
+          <t>680824</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17744</t>
+          <t>17449</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17965</t>
+          <t>17418</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39219</t>
+          <t>40197</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39695</t>
+          <t>41431</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69470</t>
+          <t>70849</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1111112</t>
+          <t>1111516</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1131894</t>
+          <t>1132189</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>786657</t>
+          <t>785679</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>807911</t>
+          <t>808458</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1906044</t>
+          <t>1904665</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1935819</t>
+          <t>1934083</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22458</t>
+          <t>21148</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10849</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27367</t>
+          <t>27063</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20285</t>
+          <t>19295</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43470</t>
+          <t>42192</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>598248</t>
+          <t>599558</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>614019</t>
+          <t>613936</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>710877</t>
+          <t>711181</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>727395</t>
+          <t>727933</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1315480</t>
+          <t>1316758</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1338665</t>
+          <t>1339655</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>924</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>7840</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10751</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27916</t>
+          <t>28491</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13282</t>
+          <t>12610</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31347</t>
+          <t>33122</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279153</t>
+          <t>279305</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286212</t>
+          <t>286221</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1054109</t>
+          <t>1053534</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1071612</t>
+          <t>1071274</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1337823</t>
+          <t>1336048</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1355888</t>
+          <t>1356560</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52556</t>
+          <t>53314</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85737</t>
+          <t>88225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>62800</t>
+          <t>62684</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100349</t>
+          <t>98738</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>126693</t>
+          <t>123887</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>177745</t>
+          <t>177038</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3299985</t>
+          <t>3297497</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3333166</t>
+          <t>3332408</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3431247</t>
+          <t>3432858</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3468796</t>
+          <t>3468912</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6739573</t>
+          <t>6740280</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6790625</t>
+          <t>6793431</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14397</t>
+          <t>15373</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18407</t>
+          <t>19820</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11742</t>
+          <t>13435</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26326</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25807</t>
+          <t>27937</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17529</t>
+          <t>19585</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36131</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>497812</t>
+          <t>542501</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>490815</t>
+          <t>535245</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>501337</t>
+          <t>546655</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>429060</t>
+          <t>468591</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>421141</t>
+          <t>458433</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>435725</t>
+          <t>474976</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>926872</t>
+          <t>1011092</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>916548</t>
+          <t>1001183</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>935150</t>
+          <t>1019444</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7457</t>
+          <t>7766</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13875</t>
+          <t>14694</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12079</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14066</t>
+          <t>14601</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>8905</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22556</t>
+          <t>22007</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>444756</t>
+          <t>475446</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>438338</t>
+          <t>468518</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>448860</t>
+          <t>479287</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>375971</t>
+          <t>416308</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>370501</t>
+          <t>411062</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>379326</t>
+          <t>420054</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>820727</t>
+          <t>891754</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>812237</t>
+          <t>884348</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>826240</t>
+          <t>897450</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20889</t>
+          <t>21155</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>12970</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39539</t>
+          <t>31642</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>9328</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>15670</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>29040</t>
+          <t>30482</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10950</t>
+          <t>20665</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46144</t>
+          <t>41570</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>647375</t>
+          <t>450457</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>628725</t>
+          <t>439970</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663096</t>
+          <t>458642</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>158760</t>
+          <t>178169</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153435</t>
+          <t>171827</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162242</t>
+          <t>182316</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>806135</t>
+          <t>628627</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>789031</t>
+          <t>617539</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>824225</t>
+          <t>638444</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20733</t>
+          <t>26128</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13343</t>
+          <t>17063</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32089</t>
+          <t>41473</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21156</t>
+          <t>25498</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9766</t>
+          <t>17992</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31989</t>
+          <t>35182</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>41889</t>
+          <t>51626</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28103</t>
+          <t>38793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57068</t>
+          <t>68254</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1014086</t>
+          <t>1105715</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1002730</t>
+          <t>1090370</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1021476</t>
+          <t>1114780</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>956041</t>
+          <t>834786</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>945208</t>
+          <t>825102</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>967431</t>
+          <t>842292</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1970127</t>
+          <t>1940501</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1954948</t>
+          <t>1923873</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1983913</t>
+          <t>1953334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>17312</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>33798</t>
+          <t>34527</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23074</t>
+          <t>26184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57017</t>
+          <t>46174</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>42835</t>
+          <t>44292</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31047</t>
+          <t>34680</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64125</t>
+          <t>57069</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>464522</t>
+          <t>556716</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>456989</t>
+          <t>549169</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>468794</t>
+          <t>561369</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>805198</t>
+          <t>795600</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>781979</t>
+          <t>783953</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>815922</t>
+          <t>803943</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1269720</t>
+          <t>1352316</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1248430</t>
+          <t>1339539</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1281508</t>
+          <t>1361928</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1312555</t>
+          <t>1396608</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1312555</t>
+          <t>1396608</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1312555</t>
+          <t>1396608</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>20840</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18131</t>
+          <t>22242</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12078</t>
+          <t>14889</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26039</t>
+          <t>31924</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>26749</t>
+          <t>30327</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17632</t>
+          <t>20792</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40606</t>
+          <t>45822</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>231889</t>
+          <t>229142</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>216635</t>
+          <t>216388</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237858</t>
+          <t>235505</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>742021</t>
+          <t>820751</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>734113</t>
+          <t>811069</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>748074</t>
+          <t>828104</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>973910</t>
+          <t>1049894</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>960053</t>
+          <t>1034399</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>983027</t>
+          <t>1059429</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>74134</t>
+          <t>81016</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53336</t>
+          <t>63721</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97865</t>
+          <t>102883</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>106252</t>
+          <t>118249</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83741</t>
+          <t>101258</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130245</t>
+          <t>137515</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>180386</t>
+          <t>199265</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>149790</t>
+          <t>174200</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>212179</t>
+          <t>228541</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3300440</t>
+          <t>3359977</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3276709</t>
+          <t>3338110</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3321238</t>
+          <t>3377272</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3467051</t>
+          <t>3514206</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3443058</t>
+          <t>3494940</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3489562</t>
+          <t>3531197</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6767491</t>
+          <t>6874184</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6735698</t>
+          <t>6844908</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6798087</t>
+          <t>6899249</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3374574</t>
+          <t>3440993</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3374574</t>
+          <t>3440993</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3374574</t>
+          <t>3440993</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573303</t>
+          <t>3632455</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573303</t>
+          <t>3632455</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573303</t>
+          <t>3632455</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6947877</t>
+          <t>7073449</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6947877</t>
+          <t>7073449</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6947877</t>
+          <t>7073449</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
